--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V842"/>
+  <dimension ref="A1:V844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81018,10 +81018,8 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A835" t="n">
+        <v>2728</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
@@ -81073,7 +81071,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N835" s="2" t="n">
+      <c r="N835" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="O835" t="inlineStr">
@@ -81114,10 +81112,8 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
+      <c r="A836" t="n">
+        <v>2731</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
@@ -81171,7 +81167,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N836" s="2" t="n">
+      <c r="N836" s="1" t="n">
         <v>43171</v>
       </c>
       <c r="O836" t="inlineStr">
@@ -81212,10 +81208,8 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A837" t="n">
+        <v>2834</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
@@ -81267,7 +81261,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N837" s="2" t="n">
+      <c r="N837" s="1" t="n">
         <v>46230</v>
       </c>
       <c r="O837" t="inlineStr">
@@ -81308,10 +81302,8 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A838" t="n">
+        <v>2834</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
@@ -81363,7 +81355,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N838" s="2" t="n">
+      <c r="N838" s="1" t="n">
         <v>46230</v>
       </c>
       <c r="O838" t="inlineStr">
@@ -81404,10 +81396,8 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A839" t="n">
+        <v>3302</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
@@ -81459,7 +81449,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N839" s="2" t="n">
+      <c r="N839" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="O839" t="inlineStr">
@@ -81500,10 +81490,8 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
+      <c r="A840" t="n">
+        <v>3713</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
@@ -81555,7 +81543,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N840" s="2" t="n">
+      <c r="N840" s="1" t="n">
         <v>44384</v>
       </c>
       <c r="O840" t="inlineStr">
@@ -81596,10 +81584,8 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" t="inlineStr">
-        <is>
-          <t>5802</t>
-        </is>
+      <c r="A841" t="n">
+        <v>5802</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
@@ -81653,7 +81639,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N841" s="2" t="n">
+      <c r="N841" s="1" t="n">
         <v>43557</v>
       </c>
       <c r="O841" t="inlineStr">
@@ -81694,10 +81680,8 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" t="inlineStr">
-        <is>
-          <t>9943</t>
-        </is>
+      <c r="A842" t="n">
+        <v>9943</v>
       </c>
       <c r="B842" t="inlineStr">
         <is>
@@ -81749,7 +81733,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N842" s="2" t="n">
+      <c r="N842" s="1" t="n">
         <v>46245</v>
       </c>
       <c r="O842" t="inlineStr">
@@ -81784,6 +81768,198 @@
         </is>
       </c>
       <c r="V842" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F843" t="n">
+        <v>119607</v>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>Presencial-Virtual</t>
+        </is>
+      </c>
+      <c r="I843" t="n">
+        <v>180</v>
+      </c>
+      <c r="J843" t="n">
+        <v>9</v>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr"/>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N843" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q843" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R843" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S843" t="inlineStr"/>
+      <c r="T843" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U843" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V843" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>UNIDADES TECNOLOGICAS DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F844" t="n">
+        <v>119105</v>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I844" t="n">
+        <v>160</v>
+      </c>
+      <c r="J844" t="n">
+        <v>10</v>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr"/>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N844" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q844" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R844" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S844" t="inlineStr"/>
+      <c r="T844" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U844" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V844" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V844"/>
+  <dimension ref="A1:V855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81774,10 +81774,8 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A843" t="n">
+        <v>1711</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
@@ -81829,7 +81827,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N843" s="2" t="n">
+      <c r="N843" s="1" t="n">
         <v>46260</v>
       </c>
       <c r="O843" t="inlineStr">
@@ -81870,10 +81868,8 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
+      <c r="A844" t="n">
+        <v>3201</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
@@ -81925,7 +81921,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N844" s="2" t="n">
+      <c r="N844" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O844" t="inlineStr">
@@ -81960,6 +81956,1062 @@
         </is>
       </c>
       <c r="V844" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F845" t="n">
+        <v>119620</v>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>Ingeniería en Inteligencia Artificial y Ciencia de datos</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I845" t="n">
+        <v>136</v>
+      </c>
+      <c r="J845" t="n">
+        <v>4</v>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr"/>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N845" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P845" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q845" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R845" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S845" t="inlineStr"/>
+      <c r="T845" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U845" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V845" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F846" t="n">
+        <v>119619</v>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>Licenciatura en Etnoeducación y Ciencias Sociales</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I846" t="n">
+        <v>152</v>
+      </c>
+      <c r="J846" t="n">
+        <v>10</v>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr"/>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N846" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a educación</t>
+        </is>
+      </c>
+      <c r="Q846" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a educación</t>
+        </is>
+      </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S846" t="inlineStr"/>
+      <c r="T846" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U846" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V846" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INDUSTRIAL DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Barbosa</t>
+        </is>
+      </c>
+      <c r="F847" t="n">
+        <v>119626</v>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>Ingeniería de Alimentos</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I847" t="n">
+        <v>128</v>
+      </c>
+      <c r="J847" t="n">
+        <v>8</v>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr"/>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N847" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q847" t="inlineStr">
+        <is>
+          <t>Procesamiento de alimentos</t>
+        </is>
+      </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S847" t="inlineStr"/>
+      <c r="T847" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U847" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V847" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL MAGDALENA - UNIMAGDALENA</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F848" t="n">
+        <v>119588</v>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>Artes Musicales</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>Híbrida (A distancia-Virtual)</t>
+        </is>
+      </c>
+      <c r="I848" t="n">
+        <v>156</v>
+      </c>
+      <c r="J848" t="n">
+        <v>9</v>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr"/>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N848" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P848" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q848" t="inlineStr">
+        <is>
+          <t>Música y artes escénicas</t>
+        </is>
+      </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="S848" t="inlineStr"/>
+      <c r="T848" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U848" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V848" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F849" t="n">
+        <v>119599</v>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I849" t="n">
+        <v>160</v>
+      </c>
+      <c r="J849" t="n">
+        <v>9</v>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr"/>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N849" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P849" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q849" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S849" t="inlineStr"/>
+      <c r="T849" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U849" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V849" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA - ITM</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F850" t="n">
+        <v>119616</v>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>INGENIERIA DE PRODUCCIÓN</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I850" t="n">
+        <v>147</v>
+      </c>
+      <c r="J850" t="n">
+        <v>9</v>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr"/>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N850" s="2" t="n">
+        <v>45155</v>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P850" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q850" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R850" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S850" t="inlineStr"/>
+      <c r="T850" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U850" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V850" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA EAM</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F851" t="n">
+        <v>115820</v>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>Negocios Digitales</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I851" t="n">
+        <v>137</v>
+      </c>
+      <c r="J851" t="n">
+        <v>8</v>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr"/>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N851" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="O851" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P851" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q851" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R851" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S851" t="inlineStr"/>
+      <c r="T851" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U851" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V851" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SAN MATEO - SAN MATEO EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F852" t="n">
+        <v>119625</v>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>INGENIERIA  AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I852" t="n">
+        <v>151</v>
+      </c>
+      <c r="J852" t="n">
+        <v>9</v>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr"/>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N852" s="2" t="n">
+        <v>44040</v>
+      </c>
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P852" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q852" t="inlineStr">
+        <is>
+          <t>Tecnología de protección del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S852" t="inlineStr"/>
+      <c r="T852" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U852" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V852" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F853" t="n">
+        <v>115814</v>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN E INNOVACIÓN EN TURISMO Y HOTELES</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I853" t="n">
+        <v>162</v>
+      </c>
+      <c r="J853" t="n">
+        <v>9</v>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr"/>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N853" s="2" t="n">
+        <v>44138</v>
+      </c>
+      <c r="O853" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P853" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q853" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R853" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S853" t="inlineStr"/>
+      <c r="T853" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U853" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V853" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F854" t="n">
+        <v>111795</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN E INNOVACIÓN EN TURISMO Y HOTELES</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I854" t="n">
+        <v>162</v>
+      </c>
+      <c r="J854" t="n">
+        <v>9</v>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr"/>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N854" s="2" t="n">
+        <v>44138</v>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P854" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q854" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S854" t="inlineStr"/>
+      <c r="T854" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U854" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V854" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>9934</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>CENTRO DE ESTUDIOS AERONÁUTICOS - CEA</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F855" t="n">
+        <v>119604</v>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>CIENCIAS AERONÁUTICAS</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I855" t="n">
+        <v>137</v>
+      </c>
+      <c r="J855" t="n">
+        <v>8</v>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr"/>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N855" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q855" t="inlineStr">
+        <is>
+          <t>Vehículos, barcos y aeronaves de motor</t>
+        </is>
+      </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>Ingeniería mecánica y afines</t>
+        </is>
+      </c>
+      <c r="S855" t="inlineStr"/>
+      <c r="T855" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U855" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V855" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V855"/>
+  <dimension ref="A1:V866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81962,10 +81962,8 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A845" t="n">
+        <v>1110</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
@@ -82017,7 +82015,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N845" s="2" t="n">
+      <c r="N845" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O845" t="inlineStr">
@@ -82058,10 +82056,8 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A846" t="n">
+        <v>1110</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
@@ -82113,7 +82109,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N846" s="2" t="n">
+      <c r="N846" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O846" t="inlineStr">
@@ -82154,10 +82150,8 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A847" t="n">
+        <v>1204</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
@@ -82209,7 +82203,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N847" s="2" t="n">
+      <c r="N847" s="1" t="n">
         <v>46252</v>
       </c>
       <c r="O847" t="inlineStr">
@@ -82250,10 +82244,8 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A848" t="n">
+        <v>1213</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
@@ -82305,7 +82297,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N848" s="2" t="n">
+      <c r="N848" s="1" t="n">
         <v>46244</v>
       </c>
       <c r="O848" t="inlineStr">
@@ -82346,10 +82338,8 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A849" t="n">
+        <v>1828</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
@@ -82401,7 +82391,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N849" s="2" t="n">
+      <c r="N849" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="O849" t="inlineStr">
@@ -82442,10 +82432,8 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A850" t="n">
+        <v>3302</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
@@ -82497,7 +82485,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N850" s="2" t="n">
+      <c r="N850" s="1" t="n">
         <v>45155</v>
       </c>
       <c r="O850" t="inlineStr">
@@ -82538,10 +82526,8 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
+      <c r="A851" t="n">
+        <v>4709</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
@@ -82593,7 +82579,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N851" s="2" t="n">
+      <c r="N851" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O851" t="inlineStr">
@@ -82634,10 +82620,8 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
+      <c r="A852" t="n">
+        <v>4726</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
@@ -82689,7 +82673,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N852" s="2" t="n">
+      <c r="N852" s="1" t="n">
         <v>44040</v>
       </c>
       <c r="O852" t="inlineStr">
@@ -82730,10 +82714,8 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A853" t="n">
+        <v>9119</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
@@ -82785,7 +82767,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N853" s="2" t="n">
+      <c r="N853" s="1" t="n">
         <v>44138</v>
       </c>
       <c r="O853" t="inlineStr">
@@ -82826,10 +82808,8 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A854" t="n">
+        <v>9119</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
@@ -82881,7 +82861,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N854" s="2" t="n">
+      <c r="N854" s="1" t="n">
         <v>44138</v>
       </c>
       <c r="O854" t="inlineStr">
@@ -82922,10 +82902,8 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" t="inlineStr">
-        <is>
-          <t>9934</t>
-        </is>
+      <c r="A855" t="n">
+        <v>9934</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
@@ -82977,7 +82955,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N855" s="2" t="n">
+      <c r="N855" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="O855" t="inlineStr">
@@ -83012,6 +82990,1064 @@
         </is>
       </c>
       <c r="V855" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F856" t="n">
+        <v>119634</v>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACIÓN BÁSICA PRIMARIA CON ÉNFASIS EN INGLÉS</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I856" t="n">
+        <v>146</v>
+      </c>
+      <c r="J856" t="n">
+        <v>9</v>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr"/>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N856" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P856" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q856" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S856" t="inlineStr"/>
+      <c r="T856" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U856" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V856" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F857" t="n">
+        <v>119635</v>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACIÓN CAMPESINA Y RURAL</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I857" t="n">
+        <v>131</v>
+      </c>
+      <c r="J857" t="n">
+        <v>8</v>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr"/>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N857" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P857" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q857" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S857" t="inlineStr"/>
+      <c r="T857" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U857" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V857" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F858" t="n">
+        <v>119628</v>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>Nutrición y Dietética</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I858" t="n">
+        <v>153</v>
+      </c>
+      <c r="J858" t="n">
+        <v>8</v>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr"/>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N858" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P858" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q858" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>Nutrición y dietética</t>
+        </is>
+      </c>
+      <c r="S858" t="inlineStr"/>
+      <c r="T858" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U858" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V858" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>UNIDAD CENTRAL DEL VALLE DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="F859" t="n">
+        <v>119667</v>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>Profesional en Música</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I859" t="n">
+        <v>159</v>
+      </c>
+      <c r="J859" t="n">
+        <v>10</v>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr"/>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N859" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P859" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q859" t="inlineStr">
+        <is>
+          <t>Música y artes escénicas</t>
+        </is>
+      </c>
+      <c r="R859" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="S859" t="inlineStr"/>
+      <c r="T859" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U859" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V859" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD FUCS</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F860" t="n">
+        <v>119650</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I860" t="n">
+        <v>136</v>
+      </c>
+      <c r="J860" t="n">
+        <v>8</v>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr"/>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N860" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q860" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S860" t="inlineStr"/>
+      <c r="T860" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U860" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V860" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F861" t="n">
+        <v>105016</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I861" t="n">
+        <v>158</v>
+      </c>
+      <c r="J861" t="n">
+        <v>9</v>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L861" t="n">
+        <v>4660000</v>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N861" s="2" t="n">
+        <v>42292</v>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P861" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q861" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S861" t="inlineStr"/>
+      <c r="T861" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U861" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V861" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DE BARRANQUILLA - IUB</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F862" t="n">
+        <v>119632</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>FINANZAS Y BANCAS</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I862" t="n">
+        <v>162</v>
+      </c>
+      <c r="J862" t="n">
+        <v>13</v>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr"/>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N862" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P862" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q862" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S862" t="inlineStr"/>
+      <c r="T862" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U862" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V862" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA ANTONIO JOSE CAMACHO</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Candelaria</t>
+        </is>
+      </c>
+      <c r="F863" t="n">
+        <v>119641</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>Presencial-Virtual</t>
+        </is>
+      </c>
+      <c r="I863" t="n">
+        <v>151</v>
+      </c>
+      <c r="J863" t="n">
+        <v>10</v>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr"/>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N863" s="2" t="n">
+        <v>45076</v>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P863" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q863" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R863" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S863" t="inlineStr"/>
+      <c r="T863" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U863" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V863" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>CORPORACION TECNOLOGICA INDUSTRIAL COLOMBIANA - TEINCO</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Mosquera</t>
+        </is>
+      </c>
+      <c r="F864" t="n">
+        <v>119663</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>INGENIERÍA MECATRÓNICA</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I864" t="n">
+        <v>157</v>
+      </c>
+      <c r="J864" t="n">
+        <v>9</v>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr"/>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N864" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P864" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q864" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>Ingeniería mecánica y afines</t>
+        </is>
+      </c>
+      <c r="S864" t="inlineStr"/>
+      <c r="T864" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U864" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V864" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA TALLER CINCO CENTRO DE DISEÑO</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F865" t="n">
+        <v>119637</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>ANIMACION</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I865" t="n">
+        <v>136</v>
+      </c>
+      <c r="J865" t="n">
+        <v>8</v>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr"/>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N865" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q865" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R865" t="inlineStr">
+        <is>
+          <t>Artes plásticas, visuales y afines</t>
+        </is>
+      </c>
+      <c r="S865" t="inlineStr"/>
+      <c r="T865" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U865" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V865" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>9938</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA DEL CHICAMOCHA</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F866" t="n">
+        <v>119666</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>Comunicación Audiovisual</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I866" t="n">
+        <v>128</v>
+      </c>
+      <c r="J866" t="n">
+        <v>8</v>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr"/>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N866" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P866" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q866" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S866" t="inlineStr"/>
+      <c r="T866" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U866" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V866" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V866"/>
+  <dimension ref="A1:V877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82996,10 +82996,8 @@
       </c>
     </row>
     <row r="856">
-      <c r="A856" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A856" t="n">
+        <v>1112</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
@@ -83051,7 +83049,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N856" s="2" t="n">
+      <c r="N856" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O856" t="inlineStr">
@@ -83092,10 +83090,8 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A857" t="n">
+        <v>1112</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
@@ -83147,7 +83143,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N857" s="2" t="n">
+      <c r="N857" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O857" t="inlineStr">
@@ -83188,10 +83184,8 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A858" t="n">
+        <v>1711</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
@@ -83243,7 +83237,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N858" s="2" t="n">
+      <c r="N858" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O858" t="inlineStr">
@@ -83284,10 +83278,8 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="A859" t="n">
+        <v>2301</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
@@ -83339,7 +83331,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N859" s="2" t="n">
+      <c r="N859" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="O859" t="inlineStr">
@@ -83380,10 +83372,8 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
+      <c r="A860" t="n">
+        <v>2702</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -83435,7 +83425,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N860" s="2" t="n">
+      <c r="N860" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O860" t="inlineStr">
@@ -83476,10 +83466,8 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A861" t="n">
+        <v>2728</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
@@ -83533,7 +83521,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N861" s="2" t="n">
+      <c r="N861" s="1" t="n">
         <v>42292</v>
       </c>
       <c r="O861" t="inlineStr">
@@ -83574,10 +83562,8 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
+      <c r="A862" t="n">
+        <v>3117</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
@@ -83629,7 +83615,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N862" s="2" t="n">
+      <c r="N862" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O862" t="inlineStr">
@@ -83670,10 +83656,8 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
+      <c r="A863" t="n">
+        <v>3301</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -83725,7 +83709,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N863" s="2" t="n">
+      <c r="N863" s="1" t="n">
         <v>45076</v>
       </c>
       <c r="O863" t="inlineStr">
@@ -83766,10 +83750,8 @@
       </c>
     </row>
     <row r="864">
-      <c r="A864" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
+      <c r="A864" t="n">
+        <v>3819</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
@@ -83821,7 +83803,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N864" s="2" t="n">
+      <c r="N864" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="O864" t="inlineStr">
@@ -83862,10 +83844,8 @@
       </c>
     </row>
     <row r="865">
-      <c r="A865" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
+      <c r="A865" t="n">
+        <v>4835</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
@@ -83917,7 +83897,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N865" s="2" t="n">
+      <c r="N865" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O865" t="inlineStr">
@@ -83958,10 +83938,8 @@
       </c>
     </row>
     <row r="866">
-      <c r="A866" t="inlineStr">
-        <is>
-          <t>9938</t>
-        </is>
+      <c r="A866" t="n">
+        <v>9938</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
@@ -84013,7 +83991,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N866" s="2" t="n">
+      <c r="N866" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="O866" t="inlineStr">
@@ -84048,6 +84026,1062 @@
         </is>
       </c>
       <c r="V866" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD TECNOLOGICA DE PEREIRA - UTP</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F867" t="n">
+        <v>119685</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I867" t="n">
+        <v>156</v>
+      </c>
+      <c r="J867" t="n">
+        <v>9</v>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr"/>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N867" s="2" t="n">
+        <v>45643</v>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P867" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q867" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S867" t="inlineStr"/>
+      <c r="T867" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U867" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V867" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD AUTONOMA DE COLOMBIA -FUAC-</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F868" t="n">
+        <v>119678</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>INGENIERÍA iNDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I868" t="n">
+        <v>144</v>
+      </c>
+      <c r="J868" t="n">
+        <v>8</v>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr"/>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N868" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P868" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q868" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S868" t="inlineStr"/>
+      <c r="T868" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U868" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V868" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MANUELA BELTRAN-UMB-</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F869" t="n">
+        <v>119694</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>INGENIERIA AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I869" t="n">
+        <v>148</v>
+      </c>
+      <c r="J869" t="n">
+        <v>8</v>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr"/>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N869" s="2" t="n">
+        <v>44433</v>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q869" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R869" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S869" t="inlineStr"/>
+      <c r="T869" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U869" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V869" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSIDAD DEL SINU - ELIAS BECHARA ZAINUM - UNISINU -</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F870" t="n">
+        <v>115811</v>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I870" t="n">
+        <v>168</v>
+      </c>
+      <c r="J870" t="n">
+        <v>9</v>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr"/>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N870" s="2" t="n">
+        <v>44656</v>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q870" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S870" t="inlineStr"/>
+      <c r="T870" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U870" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V870" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD FUCS</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F871" t="n">
+        <v>119706</v>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>Administración de Transformación Digital en Salud</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I871" t="n">
+        <v>139</v>
+      </c>
+      <c r="J871" t="n">
+        <v>8</v>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr"/>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N871" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q871" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S871" t="inlineStr"/>
+      <c r="T871" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U871" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V871" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA LOS LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F872" t="n">
+        <v>119699</v>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>ECONOMIA</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I872" t="n">
+        <v>144</v>
+      </c>
+      <c r="J872" t="n">
+        <v>8</v>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr"/>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N872" s="2" t="n">
+        <v>44271</v>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q872" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R872" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S872" t="inlineStr"/>
+      <c r="T872" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U872" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V872" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2811</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ESCUELA COLOMBIANA DE INGENIERIA JULIO GARAVITO</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F873" t="n">
+        <v>119689</v>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>NEGOCIOS DIGITALES CON ÉNFASIS EN CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I873" t="n">
+        <v>142</v>
+      </c>
+      <c r="J873" t="n">
+        <v>8</v>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr"/>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N873" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q873" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R873" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S873" t="inlineStr"/>
+      <c r="T873" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U873" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V873" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F874" t="n">
+        <v>119679</v>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>BACTERIOLOGÍA Y LABORATORIO CLÍNICO</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I874" t="n">
+        <v>162</v>
+      </c>
+      <c r="J874" t="n">
+        <v>9</v>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr"/>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N874" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P874" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q874" t="inlineStr">
+        <is>
+          <t>Tecnología de diagnóstico y tratamiento médico</t>
+        </is>
+      </c>
+      <c r="R874" t="inlineStr">
+        <is>
+          <t>Bacteriología</t>
+        </is>
+      </c>
+      <c r="S874" t="inlineStr"/>
+      <c r="T874" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U874" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V874" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2841</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="F875" t="n">
+        <v>119686</v>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>Diseño Digital</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I875" t="n">
+        <v>136</v>
+      </c>
+      <c r="J875" t="n">
+        <v>8</v>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr"/>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N875" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P875" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q875" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R875" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S875" t="inlineStr"/>
+      <c r="T875" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U875" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V875" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA PASCUAL BRAVO</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F876" t="n">
+        <v>119701</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I876" t="n">
+        <v>160</v>
+      </c>
+      <c r="J876" t="n">
+        <v>10</v>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr"/>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N876" s="2" t="n">
+        <v>45674</v>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q876" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S876" t="inlineStr"/>
+      <c r="T876" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U876" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V876" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>3718</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>FUNDACION DE ESTUDIOS SUPERIORES COMFANORTE -F.E.S.C.-</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>San José de Cúcuta</t>
+        </is>
+      </c>
+      <c r="F877" t="n">
+        <v>119715</v>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I877" t="n">
+        <v>160</v>
+      </c>
+      <c r="J877" t="n">
+        <v>9</v>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr"/>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N877" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q877" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S877" t="inlineStr"/>
+      <c r="T877" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="U877" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V877" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V877"/>
+  <dimension ref="A1:V881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84032,10 +84032,8 @@
       </c>
     </row>
     <row r="867">
-      <c r="A867" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A867" t="n">
+        <v>1111</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
@@ -84087,7 +84085,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N867" s="2" t="n">
+      <c r="N867" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O867" t="inlineStr">
@@ -84128,10 +84126,8 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
+      <c r="A868" t="n">
+        <v>1725</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
@@ -84183,7 +84179,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N868" s="2" t="n">
+      <c r="N868" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="O868" t="inlineStr">
@@ -84224,10 +84220,8 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
+      <c r="A869" t="n">
+        <v>1735</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
@@ -84279,7 +84273,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N869" s="2" t="n">
+      <c r="N869" s="1" t="n">
         <v>44433</v>
       </c>
       <c r="O869" t="inlineStr">
@@ -84320,10 +84314,8 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
+      <c r="A870" t="n">
+        <v>1834</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
@@ -84375,7 +84367,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N870" s="2" t="n">
+      <c r="N870" s="1" t="n">
         <v>44656</v>
       </c>
       <c r="O870" t="inlineStr">
@@ -84416,10 +84408,8 @@
       </c>
     </row>
     <row r="871">
-      <c r="A871" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
+      <c r="A871" t="n">
+        <v>2702</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
@@ -84471,7 +84461,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N871" s="2" t="n">
+      <c r="N871" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="O871" t="inlineStr">
@@ -84512,10 +84502,8 @@
       </c>
     </row>
     <row r="872">
-      <c r="A872" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
+      <c r="A872" t="n">
+        <v>2713</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
@@ -84567,7 +84555,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N872" s="2" t="n">
+      <c r="N872" s="1" t="n">
         <v>44271</v>
       </c>
       <c r="O872" t="inlineStr">
@@ -84608,10 +84596,8 @@
       </c>
     </row>
     <row r="873">
-      <c r="A873" t="inlineStr">
-        <is>
-          <t>2811</t>
-        </is>
+      <c r="A873" t="n">
+        <v>2811</v>
       </c>
       <c r="B873" t="inlineStr">
         <is>
@@ -84663,7 +84649,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N873" s="2" t="n">
+      <c r="N873" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O873" t="inlineStr">
@@ -84704,10 +84690,8 @@
       </c>
     </row>
     <row r="874">
-      <c r="A874" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
+      <c r="A874" t="n">
+        <v>2825</v>
       </c>
       <c r="B874" t="inlineStr">
         <is>
@@ -84759,7 +84743,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N874" s="2" t="n">
+      <c r="N874" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O874" t="inlineStr">
@@ -84800,10 +84784,8 @@
       </c>
     </row>
     <row r="875">
-      <c r="A875" t="inlineStr">
-        <is>
-          <t>2841</t>
-        </is>
+      <c r="A875" t="n">
+        <v>2841</v>
       </c>
       <c r="B875" t="inlineStr">
         <is>
@@ -84855,7 +84837,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N875" s="2" t="n">
+      <c r="N875" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="O875" t="inlineStr">
@@ -84896,10 +84878,8 @@
       </c>
     </row>
     <row r="876">
-      <c r="A876" t="inlineStr">
-        <is>
-          <t>3107</t>
-        </is>
+      <c r="A876" t="n">
+        <v>3107</v>
       </c>
       <c r="B876" t="inlineStr">
         <is>
@@ -84951,7 +84931,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N876" s="2" t="n">
+      <c r="N876" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="O876" t="inlineStr">
@@ -84992,10 +84972,8 @@
       </c>
     </row>
     <row r="877">
-      <c r="A877" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
+      <c r="A877" t="n">
+        <v>3718</v>
       </c>
       <c r="B877" t="inlineStr">
         <is>
@@ -85047,7 +85025,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N877" s="2" t="n">
+      <c r="N877" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="O877" t="inlineStr">
@@ -85082,6 +85060,390 @@
         </is>
       </c>
       <c r="V877" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F878" t="n">
+        <v>119728</v>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>Comunicación Audiovisual y Digital</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I878" t="n">
+        <v>144</v>
+      </c>
+      <c r="J878" t="n">
+        <v>8</v>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr"/>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N878" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q878" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>Artes plásticas, visuales y afines</t>
+        </is>
+      </c>
+      <c r="S878" t="inlineStr"/>
+      <c r="T878" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U878" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V878" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F879" t="n">
+        <v>119727</v>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>Diseño Estratégico</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I879" t="n">
+        <v>144</v>
+      </c>
+      <c r="J879" t="n">
+        <v>8</v>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr"/>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N879" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q879" t="inlineStr">
+        <is>
+          <t>Bellas artes</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S879" t="inlineStr"/>
+      <c r="T879" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U879" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V879" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F880" t="n">
+        <v>119690</v>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>Licenciatura en lenguas extranjeras</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I880" t="n">
+        <v>145</v>
+      </c>
+      <c r="J880" t="n">
+        <v>8</v>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr"/>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N880" s="2" t="n">
+        <v>43670</v>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q880" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S880" t="inlineStr"/>
+      <c r="T880" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U880" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V880" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F881" t="n">
+        <v>119713</v>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I881" t="n">
+        <v>144</v>
+      </c>
+      <c r="J881" t="n">
+        <v>9</v>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr"/>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N881" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q881" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R881" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S881" t="inlineStr"/>
+      <c r="T881" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U881" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V881" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V881"/>
+  <dimension ref="A1:V883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85066,10 +85066,8 @@
       </c>
     </row>
     <row r="878">
-      <c r="A878" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A878" t="n">
+        <v>2728</v>
       </c>
       <c r="B878" t="inlineStr">
         <is>
@@ -85121,7 +85119,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N878" s="2" t="n">
+      <c r="N878" s="1" t="n">
         <v>46244</v>
       </c>
       <c r="O878" t="inlineStr">
@@ -85162,10 +85160,8 @@
       </c>
     </row>
     <row r="879">
-      <c r="A879" t="inlineStr">
-        <is>
-          <t>2737</t>
-        </is>
+      <c r="A879" t="n">
+        <v>2737</v>
       </c>
       <c r="B879" t="inlineStr">
         <is>
@@ -85217,7 +85213,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N879" s="2" t="n">
+      <c r="N879" s="1" t="n">
         <v>46244</v>
       </c>
       <c r="O879" t="inlineStr">
@@ -85258,10 +85254,8 @@
       </c>
     </row>
     <row r="880">
-      <c r="A880" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A880" t="n">
+        <v>2829</v>
       </c>
       <c r="B880" t="inlineStr">
         <is>
@@ -85313,7 +85307,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N880" s="2" t="n">
+      <c r="N880" s="1" t="n">
         <v>43670</v>
       </c>
       <c r="O880" t="inlineStr">
@@ -85354,10 +85348,8 @@
       </c>
     </row>
     <row r="881">
-      <c r="A881" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A881" t="n">
+        <v>2829</v>
       </c>
       <c r="B881" t="inlineStr">
         <is>
@@ -85409,7 +85401,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N881" s="2" t="n">
+      <c r="N881" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="O881" t="inlineStr">
@@ -85444,6 +85436,198 @@
         </is>
       </c>
       <c r="V881" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD FRANCISCO DE PAULA SANTANDER</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Ocaña</t>
+        </is>
+      </c>
+      <c r="F882" t="n">
+        <v>119745</v>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>Ingeniería Industrial</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I882" t="n">
+        <v>149</v>
+      </c>
+      <c r="J882" t="n">
+        <v>9</v>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr"/>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N882" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q882" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S882" t="inlineStr"/>
+      <c r="T882" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U882" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V882" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DIGITAL DE ANTIOQUIA -IU. DIGITAL</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F883" t="n">
+        <v>119734</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>PUBLICIDAD Y MARKETING DIGITAL</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I883" t="n">
+        <v>136</v>
+      </c>
+      <c r="J883" t="n">
+        <v>8</v>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr"/>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N883" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P883" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q883" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R883" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S883" t="inlineStr"/>
+      <c r="T883" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U883" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V883" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V883"/>
+  <dimension ref="A1:V885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85442,10 +85442,8 @@
       </c>
     </row>
     <row r="882">
-      <c r="A882" t="inlineStr">
-        <is>
-          <t>1210</t>
-        </is>
+      <c r="A882" t="n">
+        <v>1210</v>
       </c>
       <c r="B882" t="inlineStr">
         <is>
@@ -85497,7 +85495,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N882" s="2" t="n">
+      <c r="N882" s="1" t="n">
         <v>46245</v>
       </c>
       <c r="O882" t="inlineStr">
@@ -85538,10 +85536,8 @@
       </c>
     </row>
     <row r="883">
-      <c r="A883" t="inlineStr">
-        <is>
-          <t>9927</t>
-        </is>
+      <c r="A883" t="n">
+        <v>9927</v>
       </c>
       <c r="B883" t="inlineStr">
         <is>
@@ -85593,7 +85589,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N883" s="2" t="n">
+      <c r="N883" s="1" t="n">
         <v>46230</v>
       </c>
       <c r="O883" t="inlineStr">
@@ -85628,6 +85624,198 @@
         </is>
       </c>
       <c r="V883" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Guadalajara de Buga</t>
+        </is>
+      </c>
+      <c r="F884" t="n">
+        <v>119766</v>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I884" t="n">
+        <v>168</v>
+      </c>
+      <c r="J884" t="n">
+        <v>10</v>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr"/>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N884" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P884" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q884" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S884" t="inlineStr"/>
+      <c r="T884" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="U884" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V884" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>9946</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA PÚBLICA DE BELLO - IUPBELLO</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="F885" t="n">
+        <v>119782</v>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>Comunicación Digital</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I885" t="n">
+        <v>144</v>
+      </c>
+      <c r="J885" t="n">
+        <v>8</v>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr"/>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N885" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P885" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q885" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S885" t="inlineStr"/>
+      <c r="T885" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="U885" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V885" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
